--- a/results/link-prediction-gcn/Link/0shot/IMDB-BINARY/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/0shot/IMDB-BINARY/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.5644±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5663±0.0020</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5733±0.0080</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6039±0.0069</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5931±0.0205</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6052±0.0074</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6052±0.0074</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6052±0.0075</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5991±0.0500</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.5644±0.0000</t>
+          <t>0.6339±0.0043</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6007±0.0156</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.5590±0.0000</t>
+          <t>0.5622±0.0023</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5693±0.0034</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5668±0.0018</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6338±0.0116</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6407±0.0031</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5961±0.0456</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6454±0.0184</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6454±0.0183</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6532±0.0047</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5873±0.0332</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6005±0.0254</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5938±0.0102</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.5643±0.0000</t>
+          <t>0.5639±0.0006</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5694±0.0027</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.5651±0.0000</t>
+          <t>0.5736±0.0074</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5869±0.0153</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5992±0.0159</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6034±0.0550</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6139±0.0070</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6139±0.0070</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6139±0.0070</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5980±0.0143</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5994±0.0227</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.6437±0.0000</t>
+          <t>0.6382±0.0027</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0002</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5629±0.0011</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5635±0.0008</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.5642±0.0000</t>
+          <t>0.5637±0.0007</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.5652±0.0000</t>
+          <t>0.5653±0.0018</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.5642±0.0000</t>
+          <t>0.5637±0.0006</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.5642±0.0000</t>
+          <t>0.5637±0.0006</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.5642±0.0000</t>
+          <t>0.5637±0.0006</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.5655±0.0000</t>
+          <t>0.6038±0.0536</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.6380±0.0000</t>
+          <t>0.6661±0.0016</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.5647±0.0000</t>
+          <t>0.6029±0.0140</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.6811±0.0000</t>
+          <t>0.6029±0.0553</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5669±0.0040</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6016±0.0533</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.5986±0.0000</t>
+          <t>0.6532±0.0010</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0007</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0.5645±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.5644±0.0000</t>
+          <t>0.5697±0.0029</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.5649±0.0000</t>
+          <t>0.5746±0.0021</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5998±0.0131</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5990±0.0321</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5949±0.0439</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5987±0.0268</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6056±0.0223</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5979±0.0248</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6017±0.0535</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6029±0.0179</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6253±0.0253</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.6537±0.0000</t>
+          <t>0.6385±0.0124</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.5653±0.0000</t>
+          <t>0.5664±0.0032</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.5629±0.0000</t>
+          <t>0.5624±0.0008</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5635±0.0007</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5639±0.0006</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.6519±0.0147</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5637±0.0006</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5637±0.0006</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5637±0.0006</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5640±0.0006</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.6455±0.0000</t>
+          <t>0.6557±0.0101</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5646±0.0000</t>
+          <t>0.5639±0.0007</t>
         </is>
       </c>
     </row>
@@ -1355,457 +1355,457 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.7215±0.0000</t>
+          <t>0.7212±0.0005</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7213±0.0005</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7220±0.0009</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7244±0.0034</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7388±0.0033</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7336±0.0090</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7213±0.0005</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7394±0.0038</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7394±0.0038</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7394±0.0038</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7359±0.0210</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.7215±0.0000</t>
+          <t>0.7402±0.0024</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7376±0.0072</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.7124±0.0000</t>
+          <t>0.7182±0.0041</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7213±0.0005</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7232±0.0014</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7220±0.0007</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7512±0.0052</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7545±0.0009</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7341±0.0184</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7568±0.0085</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7568±0.0084</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7601±0.0022</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7299±0.0124</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7294±0.0054</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7342±0.0050</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.7215±0.0000</t>
+          <t>0.7212±0.0005</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7213±0.0005</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7234±0.0012</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.7219±0.0000</t>
+          <t>0.7250±0.0030</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7310±0.0067</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7366±0.0076</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7380±0.0232</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7432±0.0036</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7432±0.0036</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7432±0.0036</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7213±0.0005</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7263±0.0047</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7369±0.0104</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>0.5701±0.0000</t>
+          <t>0.5592±0.0050</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7212±0.0005</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7210±0.0004</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7203±0.0009</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7207±0.0007</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.7214±0.0000</t>
+          <t>0.7209±0.0006</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7214±0.0008</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.7213±0.0000</t>
+          <t>0.7209±0.0005</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.7213±0.0000</t>
+          <t>0.7209±0.0005</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.7213±0.0000</t>
+          <t>0.7209±0.0005</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.7216±0.0000</t>
+          <t>0.7377±0.0227</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.7477±0.0000</t>
+          <t>0.7593±0.0008</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7389±0.0062</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.6611±0.0000</t>
+          <t>0.7011±0.0282</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7213±0.0005</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7218±0.0017</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7213±0.0005</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7213±0.0005</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7213±0.0005</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7362±0.0213</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7213±0.0005</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7213±0.0005</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7213±0.0005</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7213±0.0005</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.7257±0.0000</t>
+          <t>0.7448±0.0014</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7212±0.0006</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7212±0.0005</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7213±0.0005</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.7216±0.0000</t>
+          <t>0.7234±0.0012</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.7218±0.0000</t>
+          <t>0.7250±0.0013</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7362±0.0058</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7367±0.0146</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7338±0.0179</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7363±0.0125</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7394±0.0103</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7358±0.0118</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7368±0.0222</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7284±0.0072</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7482±0.0115</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.5946±0.0000</t>
+          <t>0.5622±0.0274</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7213±0.0005</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.7218±0.0000</t>
+          <t>0.7217±0.0012</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.7202±0.0000</t>
+          <t>0.7197±0.0008</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7207±0.0006</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7211±0.0005</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7577±0.0070</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7209±0.0005</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7209±0.0005</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7209±0.0005</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7213±0.0005</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.7552±0.0000</t>
+          <t>0.7579±0.0033</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.7217±0.0000</t>
+          <t>0.7210±0.0006</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.7293±0.0000</t>
+          <t>0.7221±0.0053</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.7944±0.0000</t>
+          <t>0.7902±0.0030</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.7446±0.0000</t>
+          <t>0.7567±0.0231</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.7771±0.0000</t>
+          <t>0.7862±0.0252</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.7937±0.0000</t>
+          <t>0.8061±0.0021</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.7924±0.0000</t>
+          <t>0.8057±0.0024</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.7943±0.0000</t>
+          <t>0.7902±0.0029</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.7925±0.0000</t>
+          <t>0.8068±0.0030</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.7925±0.0000</t>
+          <t>0.8068±0.0030</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.7925±0.0000</t>
+          <t>0.8068±0.0030</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.7943±0.0000</t>
+          <t>0.7963±0.0105</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.7870±0.0000</t>
+          <t>0.8066±0.0033</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.7919±0.0000</t>
+          <t>0.8032±0.0019</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.7277±0.0000</t>
+          <t>0.7193±0.0063</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.7944±0.0000</t>
+          <t>0.7902±0.0030</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.7244±0.0000</t>
+          <t>0.7708±0.0249</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.7819±0.0000</t>
+          <t>0.7649±0.0077</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.7957±0.0000</t>
+          <t>0.8057±0.0015</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.7951±0.0000</t>
+          <t>0.8056±0.0020</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.7943±0.0000</t>
+          <t>0.7942±0.0039</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.7950±0.0000</t>
+          <t>0.8062±0.0037</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.7950±0.0000</t>
+          <t>0.8062±0.0037</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.7950±0.0000</t>
+          <t>0.8071±0.0021</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.7945±0.0000</t>
+          <t>0.7930±0.0021</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.7611±0.0000</t>
+          <t>0.7893±0.0201</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.7932±0.0000</t>
+          <t>0.8024±0.0021</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.7286±0.0000</t>
+          <t>0.7208±0.0059</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.7944±0.0000</t>
+          <t>0.7902±0.0030</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.7608±0.0000</t>
+          <t>0.7446±0.0243</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.7806±0.0000</t>
+          <t>0.7797±0.0072</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.7952±0.0000</t>
+          <t>0.8069±0.0017</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.7943±0.0000</t>
+          <t>0.8074±0.0035</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.7942±0.0000</t>
+          <t>0.7955±0.0069</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.7943±0.0000</t>
+          <t>0.8078±0.0027</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.7943±0.0000</t>
+          <t>0.8078±0.0027</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.7943±0.0000</t>
+          <t>0.8078±0.0027</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.7937±0.0000</t>
+          <t>0.7898±0.0028</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.7708±0.0000</t>
+          <t>0.8004±0.0022</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.7914±0.0000</t>
+          <t>0.8026±0.0029</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.7365±0.0000</t>
+          <t>0.7288±0.0057</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.7934±0.0000</t>
+          <t>0.7888±0.0033</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.7490±0.0000</t>
+          <t>0.7771±0.0337</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.7861±0.0000</t>
+          <t>0.7779±0.0049</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.7831±0.0000</t>
+          <t>0.8076±0.0067</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.8151±0.0000</t>
+          <t>0.8160±0.0036</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.8029±0.0000</t>
+          <t>0.7943±0.0043</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.8152±0.0000</t>
+          <t>0.8130±0.0028</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.8152±0.0000</t>
+          <t>0.8130±0.0028</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.8152±0.0000</t>
+          <t>0.8130±0.0028</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.8007±0.0000</t>
+          <t>0.8001±0.0048</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.8384±0.0000</t>
+          <t>0.8351±0.0031</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.8173±0.0000</t>
+          <t>0.8108±0.0034</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.7290±0.0000</t>
+          <t>0.7243±0.0043</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.7945±0.0000</t>
+          <t>0.7904±0.0030</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.7680±0.0000</t>
+          <t>0.7963±0.0090</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.7879±0.0000</t>
+          <t>0.7892±0.0020</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.7918±0.0000</t>
+          <t>0.7901±0.0031</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.7934±0.0000</t>
+          <t>0.7894±0.0029</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.7945±0.0000</t>
+          <t>0.7939±0.0041</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.7934±0.0000</t>
+          <t>0.7895±0.0029</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.7934±0.0000</t>
+          <t>0.7895±0.0029</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.7934±0.0000</t>
+          <t>0.7895±0.0029</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.7944±0.0000</t>
+          <t>0.7898±0.0033</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.7979±0.0000</t>
+          <t>0.7995±0.0051</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.7900±0.0000</t>
+          <t>0.7899±0.0005</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.7285±0.0000</t>
+          <t>0.7211±0.0055</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.7944±0.0000</t>
+          <t>0.7902±0.0030</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.7467±0.0000</t>
+          <t>0.7730±0.0188</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.7622±0.0000</t>
+          <t>0.7788±0.0142</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.7948±0.0000</t>
+          <t>0.8040±0.0027</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.7941±0.0000</t>
+          <t>0.8031±0.0069</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.7943±0.0000</t>
+          <t>0.7954±0.0065</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.7941±0.0000</t>
+          <t>0.8035±0.0050</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.7941±0.0000</t>
+          <t>0.8058±0.0035</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.7941±0.0000</t>
+          <t>0.8050±0.0041</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.7944±0.0000</t>
+          <t>0.7959±0.0054</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.7700±0.0000</t>
+          <t>0.7999±0.0065</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.7916±0.0000</t>
+          <t>0.8001±0.0028</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.7410±0.0000</t>
+          <t>0.7390±0.0014</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.7954±0.0000</t>
+          <t>0.7919±0.0028</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.7347±0.0000</t>
+          <t>0.7780±0.0148</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.7858±0.0000</t>
+          <t>0.7827±0.0115</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.8115±0.0000</t>
+          <t>0.8045±0.0093</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.8033±0.0000</t>
+          <t>0.7998±0.0057</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.7916±0.0000</t>
+          <t>0.8033±0.0022</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.8004±0.0000</t>
+          <t>0.8019±0.0040</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.8004±0.0000</t>
+          <t>0.8019±0.0040</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.8004±0.0000</t>
+          <t>0.8019±0.0040</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.7936±0.0000</t>
+          <t>0.7893±0.0030</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.8543±0.0000</t>
+          <t>0.8495±0.0036</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.8091±0.0000</t>
+          <t>0.8277±0.0037</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.8124±0.0000</t>
+          <t>0.8080±0.0031</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.8561±0.0000</t>
+          <t>0.8530±0.0022</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.7820±0.0000</t>
+          <t>0.8299±0.0144</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.8166±0.0000</t>
+          <t>0.8481±0.0161</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.8556±0.0000</t>
+          <t>0.8590±0.0023</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.8561±0.0000</t>
+          <t>0.8592±0.0026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.8559±0.0000</t>
+          <t>0.8527±0.0022</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.8574±0.0000</t>
+          <t>0.8582±0.0028</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.8574±0.0000</t>
+          <t>0.8582±0.0028</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.8574±0.0000</t>
+          <t>0.8582±0.0028</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.8558±0.0000</t>
+          <t>0.8552±0.0054</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.8318±0.0000</t>
+          <t>0.8526±0.0026</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.8529±0.0000</t>
+          <t>0.8544±0.0022</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.8117±0.0000</t>
+          <t>0.8069±0.0034</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.8561±0.0000</t>
+          <t>0.8530±0.0022</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.7547±0.0000</t>
+          <t>0.8362±0.0197</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.8407±0.0000</t>
+          <t>0.8384±0.0032</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.8588±0.0000</t>
+          <t>0.8592±0.0021</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.8573±0.0000</t>
+          <t>0.8587±0.0017</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.8559±0.0000</t>
+          <t>0.8540±0.0018</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.8573±0.0000</t>
+          <t>0.8586±0.0028</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8573±0.0000</t>
+          <t>0.8586±0.0028</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.8573±0.0000</t>
+          <t>0.8590±0.0022</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.8560±0.0000</t>
+          <t>0.8526±0.0024</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.8182±0.0000</t>
+          <t>0.8392±0.0151</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.8544±0.0000</t>
+          <t>0.8557±0.0015</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.8121±0.0000</t>
+          <t>0.8075±0.0033</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.8561±0.0000</t>
+          <t>0.8530±0.0022</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.8127±0.0000</t>
+          <t>0.8211±0.0153</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.8381±0.0000</t>
+          <t>0.8436±0.0064</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.8567±0.0000</t>
+          <t>0.8586±0.0021</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.8569±0.0000</t>
+          <t>0.8597±0.0031</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.8556±0.0000</t>
+          <t>0.8546±0.0024</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.8568±0.0000</t>
+          <t>0.8592±0.0024</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.8568±0.0000</t>
+          <t>0.8592±0.0024</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.8568±0.0000</t>
+          <t>0.8592±0.0024</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.8567±0.0000</t>
+          <t>0.8527±0.0031</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.8201±0.0000</t>
+          <t>0.8443±0.0034</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.8522±0.0000</t>
+          <t>0.8550±0.0025</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.8163±0.0000</t>
+          <t>0.8117±0.0033</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.8547±0.0000</t>
+          <t>0.8500±0.0034</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.7994±0.0000</t>
+          <t>0.8465±0.0175</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.8487±0.0000</t>
+          <t>0.8442±0.0055</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.8580±0.0000</t>
+          <t>0.8628±0.0041</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.8656±0.0000</t>
+          <t>0.8660±0.0023</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.8580±0.0000</t>
+          <t>0.8540±0.0041</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.8658±0.0000</t>
+          <t>0.8634±0.0019</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.8658±0.0000</t>
+          <t>0.8634±0.0019</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.8658±0.0000</t>
+          <t>0.8634±0.0019</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.8560±0.0000</t>
+          <t>0.8565±0.0023</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.8748±0.0000</t>
+          <t>0.8727±0.0027</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.8658±0.0000</t>
+          <t>0.8607±0.0026</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.8123±0.0000</t>
+          <t>0.8090±0.0025</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.8565±0.0000</t>
+          <t>0.8529±0.0026</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.8240±0.0000</t>
+          <t>0.8563±0.0043</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.8506±0.0000</t>
+          <t>0.8501±0.0007</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.8580±0.0000</t>
+          <t>0.8528±0.0029</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.8573±0.0000</t>
+          <t>0.8515±0.0044</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.8562±0.0000</t>
+          <t>0.8538±0.0021</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.8573±0.0000</t>
+          <t>0.8532±0.0030</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.8573±0.0000</t>
+          <t>0.8532±0.0030</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.8573±0.0000</t>
+          <t>0.8532±0.0030</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.8561±0.0000</t>
+          <t>0.8524±0.0027</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.8427±0.0000</t>
+          <t>0.8486±0.0052</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.8517±0.0000</t>
+          <t>0.8515±0.0005</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.8120±0.0000</t>
+          <t>0.8076±0.0032</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.8561±0.0000</t>
+          <t>0.8530±0.0022</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.8031±0.0000</t>
+          <t>0.8380±0.0165</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.8340±0.0000</t>
+          <t>0.8436±0.0120</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.8568±0.0000</t>
+          <t>0.8591±0.0027</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.8573±0.0000</t>
+          <t>0.8583±0.0032</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.8557±0.0000</t>
+          <t>0.8547±0.0028</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.8573±0.0000</t>
+          <t>0.8574±0.0032</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.8573±0.0000</t>
+          <t>0.8585±0.0024</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.8573±0.0000</t>
+          <t>0.8581±0.0028</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.8559±0.0000</t>
+          <t>0.8548±0.0018</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.8228±0.0000</t>
+          <t>0.8454±0.0048</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.8526±0.0000</t>
+          <t>0.8531±0.0016</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.8156±0.0000</t>
+          <t>0.8146±0.0008</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.8549±0.0000</t>
+          <t>0.8516±0.0025</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.7469±0.0000</t>
+          <t>0.8202±0.0196</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.8426±0.0000</t>
+          <t>0.8410±0.0034</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.8644±0.0000</t>
+          <t>0.8594±0.0053</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.8591±0.0000</t>
+          <t>0.8573±0.0052</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.8530±0.0000</t>
+          <t>0.8580±0.0025</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.8586±0.0000</t>
+          <t>0.8569±0.0027</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.8586±0.0000</t>
+          <t>0.8569±0.0027</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.8586±0.0000</t>
+          <t>0.8569±0.0027</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.8566±0.0000</t>
+          <t>0.8537±0.0018</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.8854±0.0000</t>
+          <t>0.8809±0.0036</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.8629±0.0000</t>
+          <t>0.8694±0.0032</t>
         </is>
       </c>
     </row>
